--- a/incoming-freightiq/CE & SF Combined_Profit and Loss (17).xlsx
+++ b/incoming-freightiq/CE & SF Combined_Profit and Loss (17).xlsx
@@ -33,7 +33,7 @@
     <t>Profit and Loss</t>
   </si>
   <si>
-    <t>January 1-May 25, 2026</t>
+    <t>January 1-May 30, 2026</t>
   </si>
   <si>
     <t>Income</t>
@@ -429,13 +429,13 @@
     <t>Apr 2026</t>
   </si>
   <si>
-    <t>May 1-25 2026</t>
+    <t>May 1-30 2026</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Accrual Basis Tuesday, May 26, 2026 01:03 AM GMTZ</t>
+    <t>Accrual Basis Saturday, May 30, 2026 04:45 PM GMTZ</t>
   </si>
 </sst>
 </file>
@@ -1174,11 +1174,11 @@
         <v>189459.51</v>
       </c>
       <c r="F7" s="46">
-        <v>82037.65</v>
+        <v>123864.9</v>
       </c>
       <c r="G7" s="46">
         <f>B7+C7+D7+E7+F7</f>
-        <v>286492.16000000003</v>
+        <v>328319.41000000003</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="16">
@@ -1198,11 +1198,11 @@
         <v>1325895.61</v>
       </c>
       <c r="F8" s="46">
-        <v>1633933.1</v>
+        <v>1869803.06</v>
       </c>
       <c r="G8" s="46">
         <f>B8+C8+D8+E8+F8</f>
-        <v>6621776.210000001</v>
+        <v>6857646.17</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16">
@@ -1222,11 +1222,11 @@
         <v>1781.88</v>
       </c>
       <c r="F9" s="46">
-        <v>1574.86</v>
+        <v>17407.72</v>
       </c>
       <c r="G9" s="46">
         <f>B9+C9+D9+E9+F9</f>
-        <v>43102.189999999995</v>
+        <v>58935.049999999996</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16">
@@ -1246,11 +1246,11 @@
         <v>643584.16</v>
       </c>
       <c r="F10" s="46">
-        <v>569294.85</v>
+        <v>714397.91</v>
       </c>
       <c r="G10" s="46">
         <f>B10+C10+D10+E10+F10</f>
-        <v>2387227.0700000003</v>
+        <v>2532330.1300000004</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16">
@@ -1275,11 +1275,11 @@
       </c>
       <c r="F11" s="47">
         <f>F6+F7+F8+F9+F10</f>
-        <v>2286840.46</v>
+        <v>2725473.59</v>
       </c>
       <c r="G11" s="49">
         <f>B11+C11+D11+E11+F11</f>
-        <v>9338597.629999999</v>
+        <v>9777230.76</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -1309,11 +1309,11 @@
         <v>1045803.96</v>
       </c>
       <c r="F13" s="46">
-        <v>1162584.15</v>
+        <v>1341666.15</v>
       </c>
       <c r="G13" s="46">
         <f>B13+C13+D13+E13+F13</f>
-        <v>4762427.84</v>
+        <v>4941509.84</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16">
@@ -1329,11 +1329,11 @@
         <v>7437.81</v>
       </c>
       <c r="F14" s="46">
-        <v>6498.09</v>
+        <v>8227.16</v>
       </c>
       <c r="G14" s="46">
         <f>B14+C14+D14+E14+F14</f>
-        <v>17943.300000000003</v>
+        <v>19672.370000000003</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="F16" s="47">
         <f>F12+F13+F14+F15</f>
-        <v>1169082.24</v>
+        <v>1349893.3099999998</v>
       </c>
       <c r="G16" s="49">
         <f>B16+C16+D16+E16+F16</f>
-        <v>4835450.739999999</v>
+        <v>5016261.81</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16">
@@ -1407,11 +1407,11 @@
       </c>
       <c r="F17" s="47">
         <f>F11-F16</f>
-        <v>1117758.22</v>
+        <v>1375580.28</v>
       </c>
       <c r="G17" s="49">
         <f>B17+C17+D17+E17+F17</f>
-        <v>4503146.890000001</v>
+        <v>4760968.95</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -1441,11 +1441,11 @@
         <v>11682.41</v>
       </c>
       <c r="F19" s="46">
-        <v>11048.19</v>
+        <v>15350.32</v>
       </c>
       <c r="G19" s="46">
         <f>B19+C19+D19+E19+F19</f>
-        <v>52839.729999999996</v>
+        <v>57141.85999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16">
@@ -1635,10 +1635,12 @@
       <c r="E29" s="46">
         <v>4345.09</v>
       </c>
-      <c r="F29" s="45"/>
+      <c r="F29" s="46">
+        <v>665.67</v>
+      </c>
       <c r="G29" s="46">
         <f>B29+C29+D29+E29+F29</f>
-        <v>4345.09</v>
+        <v>5010.76</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="16">
@@ -1663,11 +1665,11 @@
       </c>
       <c r="F30" s="47">
         <f>F21+F22+F23+F24+F25+F26+F27+F28+F29</f>
-        <v>39070.43</v>
+        <v>39736.1</v>
       </c>
       <c r="G30" s="49">
         <f>B30+C30+D30+E30+F30</f>
-        <v>74958.98999999999</v>
+        <v>75624.66</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="16">
@@ -1739,10 +1741,12 @@
       <c r="E34" s="46">
         <v>6500.0</v>
       </c>
-      <c r="F34" s="45"/>
+      <c r="F34" s="46">
+        <v>6500.0</v>
+      </c>
       <c r="G34" s="46">
         <f>B34+C34+D34+E34+F34</f>
-        <v>66000.0</v>
+        <v>72500.0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16">
@@ -1767,11 +1771,11 @@
       </c>
       <c r="F35" s="47">
         <f>F31+F32+F33+F34</f>
-        <v>6000.0</v>
+        <v>12500.0</v>
       </c>
       <c r="G35" s="49">
         <f>B35+C35+D35+E35+F35</f>
-        <v>87000.0</v>
+        <v>93500.0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="16">
@@ -1791,11 +1795,11 @@
         <v>-3849.92</v>
       </c>
       <c r="F36" s="46">
-        <v>1441.85</v>
+        <v>1570.35</v>
       </c>
       <c r="G36" s="46">
         <f>B36+C36+D36+E36+F36</f>
-        <v>3434.64</v>
+        <v>3563.14</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="16">
@@ -1844,11 +1848,11 @@
         <v>1925.0</v>
       </c>
       <c r="F39" s="46">
-        <v>2041.31</v>
+        <v>4082.62</v>
       </c>
       <c r="G39" s="46">
         <f>B39+C39+D39+E39+F39</f>
-        <v>6347.0599999999995</v>
+        <v>8388.369999999999</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="16">
@@ -1886,11 +1890,11 @@
         <v>4000.0</v>
       </c>
       <c r="F41" s="46">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="G41" s="46">
         <f>B41+C41+D41+E41+F41</f>
-        <v>20000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="16">
@@ -1982,11 +1986,11 @@
         <v>15378.0</v>
       </c>
       <c r="F46" s="46">
-        <v>5655.0</v>
+        <v>9821.0</v>
       </c>
       <c r="G46" s="46">
         <f>B46+C46+D46+E46+F46</f>
-        <v>47848.0</v>
+        <v>52014.0</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="16">
@@ -2135,11 +2139,11 @@
       </c>
       <c r="F54" s="47">
         <f>F38+F39+F40+F41+F42+F43+F44+F45+F46+F47+F52+F53</f>
-        <v>33779.95</v>
+        <v>40987.26</v>
       </c>
       <c r="G54" s="49">
         <f>B54+C54+D54+E54+F54</f>
-        <v>133571.84999999998</v>
+        <v>140779.16</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="16">
@@ -2159,11 +2163,11 @@
         <v>915.5</v>
       </c>
       <c r="F55" s="46">
-        <v>515.25</v>
+        <v>708.75</v>
       </c>
       <c r="G55" s="46">
         <f>B55+C55+D55+E55+F55</f>
-        <v>3281.25</v>
+        <v>3474.75</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16">
@@ -2177,11 +2181,11 @@
         <v>39.76</v>
       </c>
       <c r="F56" s="46">
-        <v>141.19</v>
+        <v>164.15</v>
       </c>
       <c r="G56" s="46">
         <f>B56+C56+D56+E56+F56</f>
-        <v>180.95</v>
+        <v>203.91</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="16">
@@ -2201,11 +2205,11 @@
         <v>585.17</v>
       </c>
       <c r="F57" s="46">
-        <v>586.77</v>
+        <v>20586.77</v>
       </c>
       <c r="G57" s="46">
         <f>B57+C57+D57+E57+F57</f>
-        <v>3340.65</v>
+        <v>23340.65</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16">
@@ -2225,11 +2229,11 @@
         <v>16645.48</v>
       </c>
       <c r="F58" s="46">
-        <v>9265.77</v>
+        <v>15554.92</v>
       </c>
       <c r="G58" s="46">
         <f>B58+C58+D58+E58+F58</f>
-        <v>74736.9</v>
+        <v>81026.04999999999</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="16">
@@ -2249,11 +2253,11 @@
         <v>1620.0</v>
       </c>
       <c r="F59" s="46">
-        <v>10094.0</v>
+        <v>10274.0</v>
       </c>
       <c r="G59" s="46">
         <f>B59+C59+D59+E59+F59</f>
-        <v>14610.06</v>
+        <v>14790.06</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="16">
@@ -2273,11 +2277,11 @@
         <v>1682.5</v>
       </c>
       <c r="F60" s="46">
-        <v>34999.3</v>
+        <v>52391.8</v>
       </c>
       <c r="G60" s="46">
         <f>B60+C60+D60+E60+F60</f>
-        <v>82233.8</v>
+        <v>99626.3</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16">
@@ -2302,11 +2306,11 @@
       </c>
       <c r="F61" s="47">
         <f>F59+F60</f>
-        <v>45093.3</v>
+        <v>62665.8</v>
       </c>
       <c r="G61" s="49">
         <f>B61+C61+D61+E61+F61</f>
-        <v>96843.86</v>
+        <v>114416.36</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16">
@@ -2326,11 +2330,11 @@
         <v>4407.5</v>
       </c>
       <c r="F62" s="46">
-        <v>1926.68</v>
+        <v>2858.96</v>
       </c>
       <c r="G62" s="46">
         <f>B62+C62+D62+E62+F62</f>
-        <v>16542.81</v>
+        <v>17475.09</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="16">
@@ -2390,11 +2394,11 @@
         <v>851.95</v>
       </c>
       <c r="F65" s="46">
-        <v>219.2</v>
+        <v>379.75</v>
       </c>
       <c r="G65" s="46">
         <f>B65+C65+D65+E65+F65</f>
-        <v>3277.9300000000003</v>
+        <v>3438.4800000000005</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="16">
@@ -2471,11 +2475,11 @@
         <v>499.57</v>
       </c>
       <c r="F69" s="46">
-        <v>1603.95</v>
+        <v>3421.95</v>
       </c>
       <c r="G69" s="46">
         <f>B69+C69+D69+E69+F69</f>
-        <v>3982.92</v>
+        <v>5800.92</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="16">
@@ -2567,11 +2571,11 @@
         <v>9085.68</v>
       </c>
       <c r="F73" s="46">
-        <v>8937.17</v>
+        <v>8947.53</v>
       </c>
       <c r="G73" s="46">
         <f>B73+C73+D73+E73+F73</f>
-        <v>21958.550000000003</v>
+        <v>21968.910000000003</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="16">
@@ -2596,11 +2600,11 @@
       </c>
       <c r="F74" s="47">
         <f>F66+F67+F68+F69+F70+F71+F72+F73</f>
-        <v>21550.739999999998</v>
+        <v>23379.1</v>
       </c>
       <c r="G74" s="49">
         <f>B74+C74+D74+E74+F74</f>
-        <v>86020.98999999999</v>
+        <v>87849.35</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16">
@@ -2640,11 +2644,11 @@
         <v>2860.0</v>
       </c>
       <c r="F76" s="46">
-        <v>1530.0</v>
+        <v>1639.0</v>
       </c>
       <c r="G76" s="46">
         <f>B76+C76+D76+E76+F76</f>
-        <v>8900.5</v>
+        <v>9009.5</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="16">
@@ -2680,11 +2684,11 @@
         <v>4700.0</v>
       </c>
       <c r="F78" s="46">
-        <v>7000.0</v>
+        <v>8900.0</v>
       </c>
       <c r="G78" s="46">
         <f>B78+C78+D78+E78+F78</f>
-        <v>27700.0</v>
+        <v>29600.0</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="16">
@@ -2704,11 +2708,11 @@
         <v>1442.3</v>
       </c>
       <c r="F79" s="46">
-        <v>865.38</v>
+        <v>1153.84</v>
       </c>
       <c r="G79" s="46">
         <f>B79+C79+D79+E79+F79</f>
-        <v>5769.2</v>
+        <v>6057.66</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="16">
@@ -2728,11 +2732,11 @@
         <v>245.0</v>
       </c>
       <c r="F80" s="46">
-        <v>2710.0</v>
+        <v>10519.01</v>
       </c>
       <c r="G80" s="46">
         <f>B80+C80+D80+E80+F80</f>
-        <v>25295.0</v>
+        <v>33104.01</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="16">
@@ -2757,11 +2761,11 @@
       </c>
       <c r="F81" s="47">
         <f>F76+F77+F78+F79+F80</f>
-        <v>12105.38</v>
+        <v>22211.85</v>
       </c>
       <c r="G81" s="49">
         <f>B81+C81+D81+E81+F81</f>
-        <v>69014.70000000001</v>
+        <v>79121.17000000001</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="16">
@@ -2779,11 +2783,11 @@
         <v>664.01</v>
       </c>
       <c r="F82" s="46">
-        <v>758.73</v>
+        <v>1134.33</v>
       </c>
       <c r="G82" s="46">
         <f>B82+C82+D82+E82+F82</f>
-        <v>3271.2599999999998</v>
+        <v>3646.8599999999997</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="16">
@@ -2803,11 +2807,11 @@
         <v>1549.32</v>
       </c>
       <c r="F83" s="46">
-        <v>1200.12</v>
+        <v>1702.21</v>
       </c>
       <c r="G83" s="46">
         <f>B83+C83+D83+E83+F83</f>
-        <v>4173.139999999999</v>
+        <v>4675.23</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="16">
@@ -2838,11 +2842,11 @@
         <v>16071.75</v>
       </c>
       <c r="F85" s="46">
-        <v>18350.08</v>
+        <v>28310.65</v>
       </c>
       <c r="G85" s="46">
         <f>B85+C85+D85+E85+F85</f>
-        <v>79986.58</v>
+        <v>89947.15</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="16">
@@ -2862,11 +2866,11 @@
         <v>46935.52</v>
       </c>
       <c r="F86" s="46">
-        <v>28675.0</v>
+        <v>35300.0</v>
       </c>
       <c r="G86" s="46">
         <f>B86+C86+D86+E86+F86</f>
-        <v>178260.52</v>
+        <v>184885.52</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="16">
@@ -2907,11 +2911,11 @@
       </c>
       <c r="F88" s="47">
         <f>F84+F85+F86+F87</f>
-        <v>47025.08</v>
+        <v>63610.65</v>
       </c>
       <c r="G88" s="49">
         <f>B88+C88+D88+E88+F88</f>
-        <v>261155.65999999997</v>
+        <v>277741.23</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="16">
@@ -2949,11 +2953,11 @@
         <v>3782.17</v>
       </c>
       <c r="F90" s="46">
-        <v>5743.8</v>
+        <v>6702.1</v>
       </c>
       <c r="G90" s="46">
         <f>B90+C90+D90+E90+F90</f>
-        <v>20776.79</v>
+        <v>21735.09</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="16">
@@ -2969,11 +2973,11 @@
         <v>47146.76</v>
       </c>
       <c r="F91" s="46">
-        <v>32898.0</v>
+        <v>51335.87</v>
       </c>
       <c r="G91" s="46">
         <f>B91+C91+D91+E91+F91</f>
-        <v>90044.76000000001</v>
+        <v>108482.63</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="16">
@@ -2991,11 +2995,11 @@
         <v>4577.94</v>
       </c>
       <c r="F92" s="46">
-        <v>700.0</v>
+        <v>1683.3</v>
       </c>
       <c r="G92" s="46">
         <f>B92+C92+D92+E92+F92</f>
-        <v>6614.34</v>
+        <v>7597.64</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="16">
@@ -3026,11 +3030,11 @@
         <v>6060.32</v>
       </c>
       <c r="F94" s="46">
-        <v>4972.19</v>
+        <v>6589.84</v>
       </c>
       <c r="G94" s="46">
         <f>B94+C94+D94+E94+F94</f>
-        <v>31962.95</v>
+        <v>33580.600000000006</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="16">
@@ -3050,11 +3054,11 @@
         <v>858.88</v>
       </c>
       <c r="F95" s="46">
-        <v>667.23</v>
+        <v>881.95</v>
       </c>
       <c r="G95" s="46">
         <f>B95+C95+D95+E95+F95</f>
-        <v>4317.469999999999</v>
+        <v>4532.19</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="16">
@@ -3074,11 +3078,11 @@
         <v>55393.26</v>
       </c>
       <c r="F96" s="46">
-        <v>67302.36</v>
+        <v>84887.72</v>
       </c>
       <c r="G96" s="46">
         <f>B96+C96+D96+E96+F96</f>
-        <v>268293.91000000003</v>
+        <v>285879.27</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="16">
@@ -3098,11 +3102,11 @@
         <v>54276.79</v>
       </c>
       <c r="F97" s="46">
-        <v>61926.07</v>
+        <v>77875.3</v>
       </c>
       <c r="G97" s="46">
         <f>B97+C97+D97+E97+F97</f>
-        <v>258184.75000000003</v>
+        <v>274133.98000000004</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="16">
@@ -3205,11 +3209,11 @@
       </c>
       <c r="F102" s="47">
         <f>F97+F98+F99+F100+F101</f>
-        <v>62709.84</v>
+        <v>78659.07</v>
       </c>
       <c r="G102" s="49">
         <f>B102+C102+D102+E102+F102</f>
-        <v>309585.95</v>
+        <v>325535.18000000005</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="16">
@@ -3229,11 +3233,11 @@
         <v>136957.22</v>
       </c>
       <c r="F103" s="46">
-        <v>160788.73</v>
+        <v>201975.7</v>
       </c>
       <c r="G103" s="46">
         <f>B103+C103+D103+E103+F103</f>
-        <v>635718.9299999999</v>
+        <v>676905.8999999999</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="16">
@@ -3253,11 +3257,11 @@
         <v>48789.1</v>
       </c>
       <c r="F104" s="46">
-        <v>51510.03</v>
+        <v>63920.34</v>
       </c>
       <c r="G104" s="46">
         <f>B104+C104+D104+E104+F104</f>
-        <v>263478.07</v>
+        <v>275888.38</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="16">
@@ -3282,11 +3286,11 @@
       </c>
       <c r="F105" s="47">
         <f>F93+F94+F95+F96+F102+F103+F104</f>
-        <v>347950.38</v>
+        <v>436914.62</v>
       </c>
       <c r="G105" s="49">
         <f>B105+C105+D105+E105+F105</f>
-        <v>1513357.2799999998</v>
+        <v>1602321.52</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="16">
@@ -3306,11 +3310,11 @@
         <v>1781.75</v>
       </c>
       <c r="F106" s="46">
-        <v>2378.54</v>
+        <v>3097.17</v>
       </c>
       <c r="G106" s="46">
         <f>B106+C106+D106+E106+F106</f>
-        <v>6450.97</v>
+        <v>7169.6</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="16">
@@ -3389,11 +3393,11 @@
         <v>716.15</v>
       </c>
       <c r="F110" s="46">
-        <v>200.84</v>
+        <v>233.59</v>
       </c>
       <c r="G110" s="46">
         <f>B110+C110+D110+E110+F110</f>
-        <v>1837.6699999999998</v>
+        <v>1870.4199999999998</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="16">
@@ -3418,11 +3422,11 @@
       </c>
       <c r="F111" s="47">
         <f>F107+F108+F109+F110</f>
-        <v>3320.57</v>
+        <v>3353.32</v>
       </c>
       <c r="G111" s="49">
         <f>B111+C111+D111+E111+F111</f>
-        <v>16129.789999999999</v>
+        <v>16162.539999999999</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="16">
@@ -3453,11 +3457,11 @@
         <v>137873.05</v>
       </c>
       <c r="F113" s="46">
-        <v>110993.39</v>
+        <v>141634.81</v>
       </c>
       <c r="G113" s="46">
         <f>B113+C113+D113+E113+F113</f>
-        <v>467943.81</v>
+        <v>498585.23</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="16">
@@ -3477,11 +3481,11 @@
         <v>20932.84</v>
       </c>
       <c r="F114" s="46">
-        <v>23488.17</v>
+        <v>42542.59</v>
       </c>
       <c r="G114" s="46">
         <f>B114+C114+D114+E114+F114</f>
-        <v>128624.45</v>
+        <v>147678.87</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="16">
@@ -3501,11 +3505,11 @@
         <v>15971.33</v>
       </c>
       <c r="F115" s="46">
-        <v>4145.94</v>
+        <v>12695.94</v>
       </c>
       <c r="G115" s="46">
         <f>B115+C115+D115+E115+F115</f>
-        <v>30839.62</v>
+        <v>39389.62</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="16">
@@ -3547,11 +3551,11 @@
         <v>36295.48</v>
       </c>
       <c r="F117" s="46">
-        <v>45477.5</v>
+        <v>53844.9</v>
       </c>
       <c r="G117" s="46">
         <f>B117+C117+D117+E117+F117</f>
-        <v>152602.63</v>
+        <v>160970.03</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="16">
@@ -3595,11 +3599,11 @@
         <v>69675.85</v>
       </c>
       <c r="F119" s="46">
-        <v>33023.14</v>
+        <v>116699.27</v>
       </c>
       <c r="G119" s="46">
         <f>B119+C119+D119+E119+F119</f>
-        <v>280290.24</v>
+        <v>363966.37</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="16">
@@ -3648,11 +3652,11 @@
       </c>
       <c r="F121" s="47">
         <f>F112+F113+F114+F115+F116+F117+F118+F119+F120</f>
-        <v>220177.14999999997</v>
+        <v>370466.51999999996</v>
       </c>
       <c r="G121" s="49">
         <f>B121+C121+D121+E121+F121</f>
-        <v>1078492.7199999997</v>
+        <v>1228782.0899999999</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="16">
@@ -3672,11 +3676,11 @@
         <v>4660.23</v>
       </c>
       <c r="F122" s="46">
-        <v>2550.03</v>
+        <v>2830.03</v>
       </c>
       <c r="G122" s="46">
         <f>B122+C122+D122+E122+F122</f>
-        <v>20991.14</v>
+        <v>21271.14</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="16">
@@ -3717,11 +3721,11 @@
       </c>
       <c r="F124" s="47">
         <f>F18+F19+F20+F30+F35+F36+F37+F54+F55+F56+F57+F58+F61+F62+F63+F64+F65+F74+F75+F81+F82+F83+F88+F89+F90+F91+F92+F105+F106+F111+F121+F122+F123</f>
-        <v>852052.3</v>
+        <v>1206089.4000000001</v>
       </c>
       <c r="G124" s="49">
         <f>B124+C124+D124+E124+F124</f>
-        <v>3776100.0600000005</v>
+        <v>4130137.16</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="16">
@@ -3746,11 +3750,11 @@
       </c>
       <c r="F125" s="47">
         <f>F17-F124</f>
-        <v>265705.9199999999</v>
+        <v>169490.8799999999</v>
       </c>
       <c r="G125" s="49">
         <f>B125+C125+D125+E125+F125</f>
-        <v>727046.8300000004</v>
+        <v>630831.7900000004</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="16">
@@ -3885,11 +3889,11 @@
       </c>
       <c r="F131" s="47">
         <f>F125+F130</f>
-        <v>265705.9199999999</v>
+        <v>169490.8799999999</v>
       </c>
       <c r="G131" s="49">
         <f>B131+C131+D131+E131+F131</f>
-        <v>803686.5400000004</v>
+        <v>707471.5000000003</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="16">
